--- a/templates/MDR-GSPR对照表-v1.2.xlsx
+++ b/templates/MDR-GSPR对照表-v1.2.xlsx
@@ -260,7 +260,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -286,6 +286,14 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00FFF9E6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFEB9C"/>
+          <bgColor rgb="00FFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -843,7 +851,7 @@
     <row r="27" ht="45" customHeight="1">
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>⑦ 第 14、18、23 条各含多个独立子要求（14.1–14.7、18.1–18.8、23.1–23.4，且 23.1 内含 (a)–(k)）。用一行覆盖整条会掩盖内部差异。需要细化时，在该条下方插入行，A 列填 14.1 / 14.2…，并在备注列注明。</t>
+          <t>⑦ 第 14、18、23 条各含多个独立子要求（14.1–14.7、18.1–18.8、23.1–23.4，且 23.1 内含 (a)–(h)）。用一行覆盖整条会掩盖内部差异。需要细化时，在该条下方插入行，A 列填 14.1 / 14.2…，并在备注列注明。</t>
         </is>
       </c>
     </row>
@@ -1842,8 +1850,8 @@
       <formula>AND(LEN(TRIM($G2))&gt;0,$G2&lt;&gt;"其他",LEN(TRIM($I2))=0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E10">
-    <cfRule type="expression" priority="10" dxfId="1">
+  <conditionalFormatting sqref="A10:N10">
+    <cfRule type="expression" priority="11" dxfId="4" stopIfTrue="0">
       <formula>$E10="适用"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2466,7 +2474,7 @@
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>★ 第 23 条含 23.1–23.4，23.1 内还有 (a)–(k)。只写「标签符合要求」无法定位，建议按子条拆行。</t>
+          <t>★ 第 23 条含 23.1–23.4，23.1 内还有 (a)–(h)。只写「标签符合要求」无法定位，建议按子条拆行。</t>
         </is>
       </c>
     </row>
